--- a/time-table.xlsx
+++ b/time-table.xlsx
@@ -39,9 +39,6 @@
     <t>Login page</t>
   </si>
   <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
     <t>Constructor</t>
   </si>
   <si>
@@ -61,6 +58,9 @@
   </si>
   <si>
     <t>General time on development:</t>
+  </si>
+  <si>
+    <t>Dashboard(WIP)</t>
   </si>
 </sst>
 </file>
@@ -439,13 +439,13 @@
   <sheetData>
     <row r="1" spans="1:16" ht="23.4">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -471,7 +471,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -493,7 +493,7 @@
         <v>0.18254629629629629</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -508,34 +508,43 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5" s="6">
+        <v>4.1666666666666664E-2</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B6" s="6">
+        <v>2.0833333333333332E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="B7" s="6">
+        <v>2.5694444444444447E-2</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="6">
         <f>SUM(B3:B9)</f>
-        <v>0.25224537037037037</v>
+        <v>0.34043981481481483</v>
       </c>
     </row>
   </sheetData>

--- a/time-table.xlsx
+++ b/time-table.xlsx
@@ -60,7 +60,7 @@
     <t>General time on development:</t>
   </si>
   <si>
-    <t>Dashboard(WIP)</t>
+    <t>Dashboard</t>
   </si>
 </sst>
 </file>
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -131,6 +131,9 @@
     <xf numFmtId="21" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="46" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -524,19 +527,21 @@
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6">
-        <v>2.5694444444444447E-2</v>
+      <c r="B7" s="7">
+        <v>0.20902777777777778</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="B9" s="7"/>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="3" t="s">
@@ -544,10 +549,13 @@
       </c>
       <c r="B10" s="6">
         <f>SUM(B3:B9)</f>
-        <v>0.34043981481481483</v>
+        <v>0.52377314814814813</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B7:B9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
 </worksheet>
